--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_03.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_03.xlsx
@@ -38237,7 +38237,7 @@
         <v>3</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="408">
@@ -39647,7 +39647,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -39732,7 +39732,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -39741,7 +39741,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -39826,7 +39826,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -39835,7 +39835,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -40211,7 +40211,7 @@
         <v>2</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="429">
@@ -40305,7 +40305,7 @@
         <v>1</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="430">
@@ -40390,7 +40390,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -40399,7 +40399,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.7585</v>
+        <v>0.7665</v>
       </c>
     </row>
     <row r="431">
@@ -40587,7 +40587,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -40766,7 +40766,7 @@
         <v>0.13</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -40775,7 +40775,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.2865</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="435">
@@ -40860,7 +40860,7 @@
         <v>0</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -40869,7 +40869,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.2605000000000001</v>
+        <v>0.2785</v>
       </c>
     </row>
     <row r="436">
@@ -40954,7 +40954,7 @@
         <v>0</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -40963,7 +40963,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.162</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="437">
@@ -41339,7 +41339,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -41424,7 +41424,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -41433,7 +41433,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -41518,7 +41518,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -41527,7 +41527,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -41715,7 +41715,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -41903,7 +41903,7 @@
         <v>1</v>
       </c>
       <c r="AD446" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="447">
@@ -41988,7 +41988,7 @@
         <v>0.51</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -41997,7 +41997,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="448">
@@ -42082,7 +42082,7 @@
         <v>0.19</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -42091,7 +42091,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="449">
@@ -42458,7 +42458,7 @@
         <v>0</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -42467,7 +42467,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.2605000000000001</v>
+        <v>0.2785</v>
       </c>
     </row>
     <row r="453">
@@ -42552,7 +42552,7 @@
         <v>0</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -42561,7 +42561,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="454">
@@ -42646,7 +42646,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -42655,7 +42655,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -42843,7 +42843,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="457">
@@ -42937,7 +42937,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="458">
@@ -43022,7 +43022,7 @@
         <v>0.51</v>
       </c>
       <c r="AA458" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AB458" t="n">
         <v>0.57</v>
@@ -43031,7 +43031,7 @@
         <v>1</v>
       </c>
       <c r="AD458" t="n">
-        <v>0.618</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="459">
@@ -43116,7 +43116,7 @@
         <v>0.26</v>
       </c>
       <c r="AA459" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="AB459" t="n">
         <v>0.57</v>
@@ -43125,7 +43125,7 @@
         <v>2</v>
       </c>
       <c r="AD459" t="n">
-        <v>0.4115</v>
+        <v>0.4315</v>
       </c>
     </row>
     <row r="460">
@@ -43210,7 +43210,7 @@
         <v>0</v>
       </c>
       <c r="AA460" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="AB460" t="n">
         <v>0.4</v>
@@ -43219,7 +43219,7 @@
         <v>3</v>
       </c>
       <c r="AD460" t="n">
-        <v>0.141</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="461">
@@ -43313,7 +43313,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -43407,7 +43407,7 @@
         <v>2</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="463">
@@ -43783,7 +43783,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -43868,7 +43868,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -43877,7 +43877,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -43962,7 +43962,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -43971,7 +43971,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -44056,7 +44056,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -44065,7 +44065,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -44253,7 +44253,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -44347,7 +44347,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -44723,7 +44723,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -45184,7 +45184,7 @@
         <v>0</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -45193,7 +45193,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.2675</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="482">
@@ -45287,7 +45287,7 @@
         <v>2</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -45466,7 +45466,7 @@
         <v>0.58</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -45475,7 +45475,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="485">
@@ -45569,7 +45569,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -45936,7 +45936,7 @@
         <v>0.38</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -45945,7 +45945,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="490">
@@ -46030,7 +46030,7 @@
         <v>0</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -46039,7 +46039,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="491">
@@ -46133,7 +46133,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -46321,7 +46321,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -46509,7 +46509,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="496">
@@ -46885,7 +46885,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47261,7 +47261,7 @@
         <v>2</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="504">
@@ -47910,7 +47910,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -47919,7 +47919,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -48004,7 +48004,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -48013,7 +48013,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -48098,7 +48098,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -48107,7 +48107,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -48192,7 +48192,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -48201,7 +48201,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -48286,7 +48286,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -48295,7 +48295,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -48474,7 +48474,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -48483,7 +48483,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -48568,7 +48568,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -48577,7 +48577,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -48662,7 +48662,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -48671,7 +48671,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -48756,7 +48756,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -48765,7 +48765,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -48850,7 +48850,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -48859,7 +48859,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -48944,7 +48944,7 @@
         <v>0.85</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -48953,7 +48953,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.7985</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="522">
@@ -49038,7 +49038,7 @@
         <v>0.77</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -49047,7 +49047,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.768</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="523">
@@ -49132,7 +49132,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -49141,7 +49141,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="524">
@@ -49320,7 +49320,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -49329,7 +49329,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -49414,7 +49414,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -49423,7 +49423,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -49611,7 +49611,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -49987,7 +49987,7 @@
         <v>3</v>
       </c>
       <c r="AD532" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="533">
@@ -50175,7 +50175,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -50457,7 +50457,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -50645,7 +50645,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -51106,7 +51106,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -51115,7 +51115,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -51209,7 +51209,7 @@
         <v>2</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -51303,7 +51303,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.7294999999999999</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="547">
@@ -51491,7 +51491,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="549">
@@ -51773,7 +51773,7 @@
         <v>2</v>
       </c>
       <c r="AD551" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="552">
@@ -51961,7 +51961,7 @@
         <v>3</v>
       </c>
       <c r="AD553" t="n">
-        <v>0.7310000000000001</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="554">
@@ -52243,7 +52243,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="557">
@@ -52337,7 +52337,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -52422,7 +52422,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -52431,7 +52431,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -52516,7 +52516,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -52525,7 +52525,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -52704,7 +52704,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -52713,7 +52713,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -52798,7 +52798,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -52807,7 +52807,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -53089,7 +53089,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -53653,7 +53653,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="572">
@@ -53747,7 +53747,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -53935,7 +53935,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -54029,7 +54029,7 @@
         <v>3</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -54123,7 +54123,7 @@
         <v>2</v>
       </c>
       <c r="AD576" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="577">
@@ -54311,7 +54311,7 @@
         <v>3</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7994999999999999</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="579">
@@ -54405,7 +54405,7 @@
         <v>1</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="580">
@@ -54499,7 +54499,7 @@
         <v>2</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="581">
@@ -54687,7 +54687,7 @@
         <v>2</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.7134999999999999</v>
+        <v>0.7135</v>
       </c>
     </row>
     <row r="583">
@@ -54781,7 +54781,7 @@
         <v>3</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.6419999999999999</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="584">
@@ -54875,7 +54875,7 @@
         <v>3</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="585">
